--- a/docs/lem/files/xslope_james_bay.xlsx
+++ b/docs/lem/files/xslope_james_bay.xlsx
@@ -10943,10 +10943,10 @@
         <v>1</v>
       </c>
       <c r="B3" s="3">
-        <v>86</v>
+        <v>49</v>
       </c>
       <c r="C3" s="3">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
